--- a/data/italy/p4_modeling/2024-10-15/df_iteration_train.xlsx
+++ b/data/italy/p4_modeling/2024-10-15/df_iteration_train.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R354"/>
+  <dimension ref="A1:R404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24908,6 +24908,3462 @@
         <v>5</v>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>390</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>3</v>
+      </c>
+      <c r="D355" t="b">
+        <v>1</v>
+      </c>
+      <c r="E355" t="b">
+        <v>0</v>
+      </c>
+      <c r="F355" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G355" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H355" t="n">
+        <v>5</v>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L355" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M355" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>(2274, 29)</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>(449, 29)</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>(359, 29)</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_PPS', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_total_passes', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_PPDA', 'dif_mean_last_120_matches_KGP_against', 'dif_mean_last_120_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R355" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>391</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>3</v>
+      </c>
+      <c r="D356" t="b">
+        <v>1</v>
+      </c>
+      <c r="E356" t="b">
+        <v>0</v>
+      </c>
+      <c r="F356" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G356" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H356" t="n">
+        <v>5</v>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L356" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M356" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>(1953, 15)</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>(380, 15)</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>(304, 15)</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_start', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R356" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>392</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>3</v>
+      </c>
+      <c r="D357" t="b">
+        <v>1</v>
+      </c>
+      <c r="E357" t="b">
+        <v>0</v>
+      </c>
+      <c r="F357" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G357" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H357" t="n">
+        <v>5</v>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L357" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M357" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>(2508, 15)</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>(487, 15)</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>(389, 15)</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_start', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R357" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>394</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>3</v>
+      </c>
+      <c r="D358" t="b">
+        <v>1</v>
+      </c>
+      <c r="E358" t="b">
+        <v>0</v>
+      </c>
+      <c r="F358" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G358" t="inlineStr"/>
+      <c r="H358" t="n">
+        <v>5</v>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L358" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M358" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>(1962, 81)</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>(406, 81)</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>(325, 81)</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_PPS', 'dif_mean_last_120_matches_PPS_against', 'dif_mean_last_480_matches_PPS', 'dif_mean_last_480_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_480_matches_dead_balls_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_120_matches_total_passes', 'dif_mean_last_120_matches_total_passes_against', 'dif_mean_last_480_matches_total_passes', 'dif_mean_last_480_matches_total_passes_against', 'dif_mean_last_120_matches_yellow_cards', 'dif_mean_last_120_matches_yellow_cards_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_defensive_actions_against', 'dif_mean_last_480_matches_defensive_actions', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_120_matches_PPDA', 'dif_mean_last_120_matches_PPDA_against', 'dif_mean_last_480_matches_PPDA', 'dif_mean_last_480_matches_PPDA_against', 'dif_mean_last_120_matches_KGP', 'dif_mean_last_120_matches_KGP_against', 'dif_mean_last_480_matches_KGP', 'dif_mean_last_480_matches_KGP_against', 'dif_mean_last_120_matches_clean_sheet', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R358" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>395</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>3</v>
+      </c>
+      <c r="D359" t="b">
+        <v>1</v>
+      </c>
+      <c r="E359" t="b">
+        <v>0</v>
+      </c>
+      <c r="F359" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G359" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H359" t="n">
+        <v>5</v>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L359" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M359" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>(645, 61)</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>(120, 61)</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>(96, 61)</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_PPS', 'dif_mean_last_120_matches_PPS_against', 'dif_mean_last_480_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_120_matches_total_passes_against', 'dif_mean_last_480_matches_total_passes', 'dif_mean_last_120_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_defensive_actions_against', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_480_matches_PPDA_against', 'dif_mean_last_120_matches_KGP_against', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R359" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>396</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>3</v>
+      </c>
+      <c r="D360" t="b">
+        <v>1</v>
+      </c>
+      <c r="E360" t="b">
+        <v>0</v>
+      </c>
+      <c r="F360" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G360" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H360" t="n">
+        <v>5</v>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L360" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M360" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>(1950, 61)</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>(406, 61)</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>(325, 61)</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_PPS', 'dif_mean_last_120_matches_PPS_against', 'dif_mean_last_480_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_120_matches_total_passes_against', 'dif_mean_last_480_matches_total_passes', 'dif_mean_last_120_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_defensive_actions_against', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_480_matches_PPDA_against', 'dif_mean_last_120_matches_KGP_against', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R360" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>397</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>3</v>
+      </c>
+      <c r="D361" t="b">
+        <v>1</v>
+      </c>
+      <c r="E361" t="b">
+        <v>0</v>
+      </c>
+      <c r="F361" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G361" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H361" t="n">
+        <v>5</v>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L361" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M361" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>(786, 41)</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>(148, 41)</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>(119, 41)</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_PPS', 'dif_mean_last_120_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_120_matches_total_passes_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_480_matches_PPDA_against', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R361" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>398</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>3</v>
+      </c>
+      <c r="D362" t="b">
+        <v>1</v>
+      </c>
+      <c r="E362" t="b">
+        <v>0</v>
+      </c>
+      <c r="F362" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H362" t="n">
+        <v>5</v>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L362" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M362" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>(2073, 41)</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>(424, 41)</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>(339, 41)</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_PPS', 'dif_mean_last_120_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_120_matches_total_passes_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_480_matches_PPDA_against', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R362" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>399</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>3</v>
+      </c>
+      <c r="D363" t="b">
+        <v>1</v>
+      </c>
+      <c r="E363" t="b">
+        <v>0</v>
+      </c>
+      <c r="F363" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G363" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H363" t="n">
+        <v>5</v>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L363" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M363" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>(1314, 21)</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>(257, 21)</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>(206, 21)</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R363" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>400</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>3</v>
+      </c>
+      <c r="D364" t="b">
+        <v>1</v>
+      </c>
+      <c r="E364" t="b">
+        <v>0</v>
+      </c>
+      <c r="F364" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G364" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H364" t="n">
+        <v>5</v>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L364" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M364" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>(2289, 21)</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>(449, 21)</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>(359, 21)</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R364" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>402</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>3</v>
+      </c>
+      <c r="D365" t="b">
+        <v>1</v>
+      </c>
+      <c r="E365" t="b">
+        <v>0</v>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
+      <c r="H365" t="n">
+        <v>5</v>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L365" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M365" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>(1923, 89)</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>(390, 89)</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>(312, 89)</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_120_matches_expected_points', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_expected_points', 'dif_mean_last_480_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_120_matches_points_against', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_PPS', 'dif_mean_last_120_matches_PPS_against', 'dif_mean_last_480_matches_PPS', 'dif_mean_last_480_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_480_matches_dead_balls_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_120_matches_ball_possession_against', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession_against', 'dif_mean_last_120_matches_total_passes', 'dif_mean_last_120_matches_total_passes_against', 'dif_mean_last_480_matches_total_passes', 'dif_mean_last_480_matches_total_passes_against', 'dif_mean_last_120_matches_yellow_cards', 'dif_mean_last_120_matches_yellow_cards_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_defensive_actions_against', 'dif_mean_last_480_matches_defensive_actions', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_120_matches_PPDA', 'dif_mean_last_120_matches_PPDA_against', 'dif_mean_last_480_matches_PPDA', 'dif_mean_last_480_matches_PPDA_against', 'dif_mean_last_120_matches_KGP', 'dif_mean_last_120_matches_KGP_against', 'dif_mean_last_480_matches_KGP', 'dif_mean_last_480_matches_KGP_against', 'dif_mean_last_120_matches_clean_sheet', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R365" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>404</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>3</v>
+      </c>
+      <c r="D366" t="b">
+        <v>1</v>
+      </c>
+      <c r="E366" t="b">
+        <v>0</v>
+      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H366" t="n">
+        <v>5</v>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L366" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M366" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>(1908, 67)</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>(390, 67)</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>(312, 67)</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_120_matches_points_against', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_PPS', 'dif_mean_last_120_matches_PPS_against', 'dif_mean_last_480_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_120_matches_ball_possession_against', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession_against', 'dif_mean_last_120_matches_total_passes', 'dif_mean_last_120_matches_total_passes_against', 'dif_mean_last_480_matches_total_passes', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_defensive_actions_against', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_480_matches_PPDA', 'dif_mean_last_480_matches_PPDA_against', 'dif_mean_last_120_matches_KGP', 'dif_mean_last_120_matches_clean_sheet', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R366" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>405</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>3</v>
+      </c>
+      <c r="D367" t="b">
+        <v>1</v>
+      </c>
+      <c r="E367" t="b">
+        <v>0</v>
+      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H367" t="n">
+        <v>5</v>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L367" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M367" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>(669, 45)</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>(129, 45)</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>(104, 45)</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points_against', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_PPS_against', 'dif_mean_last_480_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_480_matches_total_passes', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_480_matches_PPDA_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R367" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>406</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>3</v>
+      </c>
+      <c r="D368" t="b">
+        <v>1</v>
+      </c>
+      <c r="E368" t="b">
+        <v>0</v>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H368" t="n">
+        <v>5</v>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L368" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M368" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>(1968, 45)</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>(406, 45)</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>(325, 45)</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points_against', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_PPS_against', 'dif_mean_last_480_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_480_matches_total_passes', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_480_matches_PPDA_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R368" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>407</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>3</v>
+      </c>
+      <c r="D369" t="b">
+        <v>1</v>
+      </c>
+      <c r="E369" t="b">
+        <v>0</v>
+      </c>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H369" t="n">
+        <v>5</v>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L369" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M369" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>(1338, 23)</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>(261, 23)</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>(209, 23)</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_total_passes', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R369" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>408</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>3</v>
+      </c>
+      <c r="D370" t="b">
+        <v>1</v>
+      </c>
+      <c r="E370" t="b">
+        <v>0</v>
+      </c>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H370" t="n">
+        <v>5</v>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L370" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M370" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>(2160, 23)</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>(433, 23)</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>(346, 23)</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_480_matches_PPS_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_total_passes', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R370" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>409</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>3</v>
+      </c>
+      <c r="D371" t="b">
+        <v>1</v>
+      </c>
+      <c r="E371" t="b">
+        <v>0</v>
+      </c>
+      <c r="F371" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="n">
+        <v>10</v>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L371" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M371" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>(1422, 48)</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>(277, 48)</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>(222, 48)</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_120_matches_yellow_cards', 'dif_mean_last_120_matches_yellow_cards_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_defensive_actions_against', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_120_matches_KGP', 'dif_mean_last_120_matches_KGP_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R371" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>410</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>3</v>
+      </c>
+      <c r="D372" t="b">
+        <v>1</v>
+      </c>
+      <c r="E372" t="b">
+        <v>0</v>
+      </c>
+      <c r="F372" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="n">
+        <v>10</v>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L372" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M372" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>(4383, 48)</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>(842, 48)</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>(674, 48)</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_120_matches_yellow_cards', 'dif_mean_last_120_matches_yellow_cards_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_defensive_actions_against', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_120_matches_KGP', 'dif_mean_last_120_matches_KGP_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R372" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>411</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>3</v>
+      </c>
+      <c r="D373" t="b">
+        <v>1</v>
+      </c>
+      <c r="E373" t="b">
+        <v>0</v>
+      </c>
+      <c r="F373" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G373" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H373" t="n">
+        <v>10</v>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L373" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M373" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>(1524, 36)</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>(297, 36)</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>(238, 36)</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_120_matches_yellow_cards_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R373" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>412</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>3</v>
+      </c>
+      <c r="D374" t="b">
+        <v>1</v>
+      </c>
+      <c r="E374" t="b">
+        <v>0</v>
+      </c>
+      <c r="F374" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G374" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H374" t="n">
+        <v>10</v>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L374" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M374" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>(4749, 36)</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>(926, 36)</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>(740, 36)</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_120_matches_yellow_cards_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R374" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>413</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>3</v>
+      </c>
+      <c r="D375" t="b">
+        <v>1</v>
+      </c>
+      <c r="E375" t="b">
+        <v>0</v>
+      </c>
+      <c r="F375" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G375" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H375" t="n">
+        <v>10</v>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L375" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M375" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>(2610, 24)</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>(522, 24)</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>(418, 24)</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R375" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>414</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>3</v>
+      </c>
+      <c r="D376" t="b">
+        <v>1</v>
+      </c>
+      <c r="E376" t="b">
+        <v>0</v>
+      </c>
+      <c r="F376" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G376" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H376" t="n">
+        <v>10</v>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L376" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M376" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>(4959, 24)</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>(961, 24)</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>(769, 24)</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R376" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>415</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>3</v>
+      </c>
+      <c r="D377" t="b">
+        <v>1</v>
+      </c>
+      <c r="E377" t="b">
+        <v>0</v>
+      </c>
+      <c r="F377" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G377" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H377" t="n">
+        <v>10</v>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L377" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M377" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>(4326, 12)</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>(842, 12)</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>(674, 12)</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_rat_player_start']</t>
+        </is>
+      </c>
+      <c r="R377" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>416</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>3</v>
+      </c>
+      <c r="D378" t="b">
+        <v>1</v>
+      </c>
+      <c r="E378" t="b">
+        <v>0</v>
+      </c>
+      <c r="F378" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G378" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H378" t="n">
+        <v>10</v>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L378" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M378" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>(5232, 12)</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>(1002, 12)</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>(802, 12)</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_rat_player_start']</t>
+        </is>
+      </c>
+      <c r="R378" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>417</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>3</v>
+      </c>
+      <c r="D379" t="b">
+        <v>1</v>
+      </c>
+      <c r="E379" t="b">
+        <v>0</v>
+      </c>
+      <c r="F379" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="n">
+        <v>10</v>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L379" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M379" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>(1434, 67)</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>(275, 67)</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>(220, 67)</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_480_matches_dead_balls_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_120_matches_yellow_cards', 'dif_mean_last_120_matches_yellow_cards_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_defensive_actions_against', 'dif_mean_last_480_matches_defensive_actions', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_120_matches_KGP', 'dif_mean_last_120_matches_KGP_against', 'dif_mean_last_120_matches_clean_sheet', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R379" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>418</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>3</v>
+      </c>
+      <c r="D380" t="b">
+        <v>1</v>
+      </c>
+      <c r="E380" t="b">
+        <v>0</v>
+      </c>
+      <c r="F380" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="n">
+        <v>10</v>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L380" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M380" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>(4416, 67)</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>(842, 67)</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>(674, 67)</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_480_matches_dead_balls_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_120_matches_yellow_cards', 'dif_mean_last_120_matches_yellow_cards_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_defensive_actions_against', 'dif_mean_last_480_matches_defensive_actions', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_120_matches_KGP', 'dif_mean_last_120_matches_KGP_against', 'dif_mean_last_120_matches_clean_sheet', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R380" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>419</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>3</v>
+      </c>
+      <c r="D381" t="b">
+        <v>1</v>
+      </c>
+      <c r="E381" t="b">
+        <v>0</v>
+      </c>
+      <c r="F381" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G381" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H381" t="n">
+        <v>10</v>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L381" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M381" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>(2607, 50)</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>(515, 50)</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>(412, 50)</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_120_matches_yellow_cards_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_480_matches_defensive_actions', 'dif_mean_last_120_matches_clean_sheet', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R381" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>420</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>3</v>
+      </c>
+      <c r="D382" t="b">
+        <v>1</v>
+      </c>
+      <c r="E382" t="b">
+        <v>0</v>
+      </c>
+      <c r="F382" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G382" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H382" t="n">
+        <v>10</v>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L382" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M382" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>(4635, 50)</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>(900, 50)</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>(720, 50)</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_120_matches_yellow_cards_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_480_matches_defensive_actions', 'dif_mean_last_120_matches_clean_sheet', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R382" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>421</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>3</v>
+      </c>
+      <c r="D383" t="b">
+        <v>1</v>
+      </c>
+      <c r="E383" t="b">
+        <v>0</v>
+      </c>
+      <c r="F383" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G383" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H383" t="n">
+        <v>10</v>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L383" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M383" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>(2601, 34)</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>(532, 34)</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>(426, 34)</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_480_matches_defensive_actions', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R383" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>422</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>3</v>
+      </c>
+      <c r="D384" t="b">
+        <v>1</v>
+      </c>
+      <c r="E384" t="b">
+        <v>0</v>
+      </c>
+      <c r="F384" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G384" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H384" t="n">
+        <v>10</v>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L384" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M384" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>(4590, 34)</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>(883, 34)</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>(706, 34)</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_480_matches_defensive_actions', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R384" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>423</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>3</v>
+      </c>
+      <c r="D385" t="b">
+        <v>1</v>
+      </c>
+      <c r="E385" t="b">
+        <v>0</v>
+      </c>
+      <c r="F385" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G385" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H385" t="n">
+        <v>10</v>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L385" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M385" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>(2958, 17)</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>(578, 17)</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>(463, 17)</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_120_matches_goals', 'dif_mean_last_480_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R385" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>424</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>3</v>
+      </c>
+      <c r="D386" t="b">
+        <v>1</v>
+      </c>
+      <c r="E386" t="b">
+        <v>0</v>
+      </c>
+      <c r="F386" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G386" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H386" t="n">
+        <v>10</v>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L386" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M386" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>(4845, 17)</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>(937, 17)</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>(749, 17)</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_120_matches_goals', 'dif_mean_last_480_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R386" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>425</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>3</v>
+      </c>
+      <c r="D387" t="b">
+        <v>1</v>
+      </c>
+      <c r="E387" t="b">
+        <v>0</v>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="n">
+        <v>10</v>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L387" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M387" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>(798, 76)</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>(177, 76)</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>(141, 76)</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_120_matches_expected_points', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_expected_points', 'dif_mean_last_480_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_120_matches_points_against', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_480_matches_dead_balls_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_120_matches_ball_possession_against', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession_against', 'dif_mean_last_120_matches_yellow_cards', 'dif_mean_last_120_matches_yellow_cards_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_defensive_actions_against', 'dif_mean_last_480_matches_defensive_actions', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_120_matches_KGP', 'dif_mean_last_120_matches_KGP_against', 'dif_mean_last_120_matches_clean_sheet', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R387" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>426</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>3</v>
+      </c>
+      <c r="D388" t="b">
+        <v>1</v>
+      </c>
+      <c r="E388" t="b">
+        <v>0</v>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="n">
+        <v>10</v>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L388" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M388" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>(4314, 76)</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>(760, 76)</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>(649, 76)</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_120_matches_expected_points', 'dif_mean_last_120_matches_expected_points_against', 'dif_mean_last_480_matches_expected_points', 'dif_mean_last_480_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_480_matches_goals_against', 'dif_mean_last_120_matches_points', 'dif_mean_last_120_matches_points_against', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_goal_ratio_against', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_480_matches_dangerous_attacks', 'dif_mean_last_480_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_dead_balls', 'dif_mean_last_480_matches_dead_balls_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_120_matches_ball_possession_against', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession_against', 'dif_mean_last_120_matches_yellow_cards', 'dif_mean_last_120_matches_yellow_cards_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_defensive_actions_against', 'dif_mean_last_480_matches_defensive_actions', 'dif_mean_last_480_matches_defensive_actions_against', 'dif_mean_last_120_matches_KGP', 'dif_mean_last_120_matches_KGP_against', 'dif_mean_last_120_matches_clean_sheet', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_last_480_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R388" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>427</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>3</v>
+      </c>
+      <c r="D389" t="b">
+        <v>1</v>
+      </c>
+      <c r="E389" t="b">
+        <v>0</v>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H389" t="n">
+        <v>10</v>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L389" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M389" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>(918, 57)</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>(196, 57)</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>(157, 57)</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_120_matches_expected_points', 'dif_mean_last_480_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_120_matches_points_against', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_120_matches_ball_possession_against', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_clean_sheet', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R389" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>428</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>3</v>
+      </c>
+      <c r="D390" t="b">
+        <v>1</v>
+      </c>
+      <c r="E390" t="b">
+        <v>0</v>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H390" t="n">
+        <v>10</v>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L390" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M390" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>(4371, 57)</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>(831, 57)</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>(665, 57)</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_120_matches_expected_points', 'dif_mean_last_480_matches_expected_points_against', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_120_matches_points_against', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_attacks', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_120_matches_ball_possession', 'dif_mean_last_120_matches_ball_possession_against', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_yellow_cards_against', 'dif_mean_last_120_matches_red_cards', 'dif_mean_last_120_matches_red_cards_against', 'dif_mean_last_480_matches_red_cards', 'dif_mean_last_480_matches_red_cards_against', 'dif_mean_last_120_matches_defensive_actions', 'dif_mean_last_120_matches_clean_sheet', 'dif_mean_last_120_matches_clean_sheet_against', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R390" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>429</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>3</v>
+      </c>
+      <c r="D391" t="b">
+        <v>1</v>
+      </c>
+      <c r="E391" t="b">
+        <v>0</v>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H391" t="n">
+        <v>10</v>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L391" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M391" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>(1848, 38)</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>(390, 38)</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>(312, 38)</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>['referee', 'is_cup', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R391" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>430</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>3</v>
+      </c>
+      <c r="D392" t="b">
+        <v>1</v>
+      </c>
+      <c r="E392" t="b">
+        <v>0</v>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H392" t="n">
+        <v>10</v>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L392" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M392" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>(4767, 38)</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>(927, 38)</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>(741, 38)</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>['referee', 'is_cup', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_shots_on_goal_against', 'dif_mean_last_480_matches_shots_on_goal', 'dif_mean_last_480_matches_shots_on_goal_against', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_120_matches_goals_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_points_against', 'dif_mean_last_120_matches_goal_ratio', 'dif_mean_last_120_matches_goal_ratio_against', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_120_matches_attacks_against', 'dif_mean_last_480_matches_attacks_against', 'dif_mean_last_120_matches_dangerous_attacks_against', 'dif_mean_last_120_matches_dead_balls', 'dif_mean_last_120_matches_dead_balls_against', 'dif_mean_last_480_matches_ball_possession', 'dif_mean_last_480_matches_ball_possession_against', 'dif_mean_last_480_matches_yellow_cards', 'dif_mean_last_480_matches_clean_sheet', 'dif_mean_last_480_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R392" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>431</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>3</v>
+      </c>
+      <c r="D393" t="b">
+        <v>1</v>
+      </c>
+      <c r="E393" t="b">
+        <v>0</v>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H393" t="n">
+        <v>10</v>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L393" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M393" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>(2928, 19)</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>(618, 19)</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>(494, 19)</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_ball_possession_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R393" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>432</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>3</v>
+      </c>
+      <c r="D394" t="b">
+        <v>1</v>
+      </c>
+      <c r="E394" t="b">
+        <v>0</v>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H394" t="n">
+        <v>10</v>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L394" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M394" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>(4695, 19)</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>(906, 19)</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>(724, 19)</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_120_matches_shots_on_goal', 'dif_mean_last_120_matches_goal_attempts_against', 'dif_mean_last_480_matches_goal_attempts', 'dif_mean_last_480_matches_goal_attempts_against', 'dif_mean_last_480_matches_goals', 'dif_mean_last_120_matches_points', 'dif_mean_last_480_matches_points', 'dif_mean_last_480_matches_goal_ratio', 'dif_mean_last_480_matches_ball_possession_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R394" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>433</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>3</v>
+      </c>
+      <c r="D395" t="b">
+        <v>0</v>
+      </c>
+      <c r="E395" t="b">
+        <v>1</v>
+      </c>
+      <c r="F395" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G395" t="inlineStr"/>
+      <c r="H395" t="n">
+        <v>3</v>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L395" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M395" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>(474, 30)</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>(90, 30)</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>(72, 30)</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R395" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>434</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>3</v>
+      </c>
+      <c r="D396" t="b">
+        <v>0</v>
+      </c>
+      <c r="E396" t="b">
+        <v>1</v>
+      </c>
+      <c r="F396" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G396" t="inlineStr"/>
+      <c r="H396" t="n">
+        <v>3</v>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L396" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M396" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>(1278, 30)</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>(244, 30)</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>(195, 30)</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R396" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>435</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>3</v>
+      </c>
+      <c r="D397" t="b">
+        <v>0</v>
+      </c>
+      <c r="E397" t="b">
+        <v>1</v>
+      </c>
+      <c r="F397" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G397" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H397" t="n">
+        <v>3</v>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L397" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M397" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>(789, 22)</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>(151, 22)</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>(121, 22)</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_PPDA', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R397" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>436</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>3</v>
+      </c>
+      <c r="D398" t="b">
+        <v>0</v>
+      </c>
+      <c r="E398" t="b">
+        <v>1</v>
+      </c>
+      <c r="F398" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G398" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H398" t="n">
+        <v>3</v>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L398" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M398" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>(1242, 22)</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>(244, 22)</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>(195, 22)</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_PPDA', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R398" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>437</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>3</v>
+      </c>
+      <c r="D399" t="b">
+        <v>0</v>
+      </c>
+      <c r="E399" t="b">
+        <v>1</v>
+      </c>
+      <c r="F399" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G399" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H399" t="n">
+        <v>3</v>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L399" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M399" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>(1122, 15)</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>(231, 15)</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>(185, 15)</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_red_cards', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start']</t>
+        </is>
+      </c>
+      <c r="R399" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>438</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>3</v>
+      </c>
+      <c r="D400" t="b">
+        <v>0</v>
+      </c>
+      <c r="E400" t="b">
+        <v>1</v>
+      </c>
+      <c r="F400" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G400" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H400" t="n">
+        <v>3</v>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L400" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M400" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>(1470, 15)</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>(282, 15)</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>(226, 15)</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_red_cards', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start']</t>
+        </is>
+      </c>
+      <c r="R400" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>439</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>3</v>
+      </c>
+      <c r="D401" t="b">
+        <v>0</v>
+      </c>
+      <c r="E401" t="b">
+        <v>1</v>
+      </c>
+      <c r="F401" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G401" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H401" t="n">
+        <v>3</v>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L401" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M401" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>(1218, 8)</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>(237, 8)</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>(190, 8)</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_rat_player_start']</t>
+        </is>
+      </c>
+      <c r="R401" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>440</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>3</v>
+      </c>
+      <c r="D402" t="b">
+        <v>0</v>
+      </c>
+      <c r="E402" t="b">
+        <v>1</v>
+      </c>
+      <c r="F402" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G402" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H402" t="n">
+        <v>3</v>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L402" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M402" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>(1458, 8)</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>(282, 8)</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>(226, 8)</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_rat_player_start']</t>
+        </is>
+      </c>
+      <c r="R402" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>441</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>3</v>
+      </c>
+      <c r="D403" t="b">
+        <v>0</v>
+      </c>
+      <c r="E403" t="b">
+        <v>1</v>
+      </c>
+      <c r="F403" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="n">
+        <v>3</v>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L403" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M403" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>(435, 42)</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>(88, 42)</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>(71, 42)</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R403" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>442</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>3</v>
+      </c>
+      <c r="D404" t="b">
+        <v>0</v>
+      </c>
+      <c r="E404" t="b">
+        <v>1</v>
+      </c>
+      <c r="F404" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="n">
+        <v>3</v>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L404" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M404" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>(1314, 42)</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>(244, 42)</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>(195, 42)</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R404" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p4_modeling/2024-10-15/df_iteration_train.xlsx
+++ b/data/italy/p4_modeling/2024-10-15/df_iteration_train.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R404"/>
+  <dimension ref="A1:R528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28364,6 +28364,8572 @@
         <v>5</v>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>443</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>3</v>
+      </c>
+      <c r="D405" t="b">
+        <v>0</v>
+      </c>
+      <c r="E405" t="b">
+        <v>1</v>
+      </c>
+      <c r="F405" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G405" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H405" t="n">
+        <v>3</v>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L405" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M405" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>(471, 31)</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>(88, 31)</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>(71, 31)</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R405" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>444</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>3</v>
+      </c>
+      <c r="D406" t="b">
+        <v>0</v>
+      </c>
+      <c r="E406" t="b">
+        <v>1</v>
+      </c>
+      <c r="F406" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G406" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H406" t="n">
+        <v>3</v>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L406" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M406" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>(1314, 31)</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>(244, 31)</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>(195, 31)</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R406" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>445</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>3</v>
+      </c>
+      <c r="D407" t="b">
+        <v>0</v>
+      </c>
+      <c r="E407" t="b">
+        <v>1</v>
+      </c>
+      <c r="F407" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G407" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H407" t="n">
+        <v>3</v>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L407" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M407" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>(1233, 21)</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>(229, 21)</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>(183, 21)</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R407" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>446</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>3</v>
+      </c>
+      <c r="D408" t="b">
+        <v>0</v>
+      </c>
+      <c r="E408" t="b">
+        <v>1</v>
+      </c>
+      <c r="F408" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G408" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H408" t="n">
+        <v>3</v>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L408" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M408" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>(1323, 21)</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>(244, 21)</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>(195, 21)</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R408" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>447</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>3</v>
+      </c>
+      <c r="D409" t="b">
+        <v>0</v>
+      </c>
+      <c r="E409" t="b">
+        <v>1</v>
+      </c>
+      <c r="F409" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G409" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H409" t="n">
+        <v>3</v>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L409" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M409" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>(1215, 11)</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>(235, 11)</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>(188, 11)</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_rat_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R409" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>448</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>3</v>
+      </c>
+      <c r="D410" t="b">
+        <v>0</v>
+      </c>
+      <c r="E410" t="b">
+        <v>1</v>
+      </c>
+      <c r="F410" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G410" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H410" t="n">
+        <v>3</v>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L410" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M410" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>(1359, 11)</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>(250, 11)</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>(200, 11)</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_rat_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R410" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>450</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>3</v>
+      </c>
+      <c r="D411" t="b">
+        <v>0</v>
+      </c>
+      <c r="E411" t="b">
+        <v>1</v>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="n">
+        <v>3</v>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L411" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M411" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>(1284, 52)</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>(242, 52)</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>(193, 52)</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R411" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>451</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>3</v>
+      </c>
+      <c r="D412" t="b">
+        <v>0</v>
+      </c>
+      <c r="E412" t="b">
+        <v>1</v>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H412" t="n">
+        <v>3</v>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L412" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M412" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>(783, 39)</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>(149, 39)</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>(120, 39)</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R412" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>452</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>3</v>
+      </c>
+      <c r="D413" t="b">
+        <v>0</v>
+      </c>
+      <c r="E413" t="b">
+        <v>1</v>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H413" t="n">
+        <v>3</v>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L413" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M413" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>(1350, 39)</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>(250, 39)</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>(200, 39)</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R413" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>453</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>3</v>
+      </c>
+      <c r="D414" t="b">
+        <v>0</v>
+      </c>
+      <c r="E414" t="b">
+        <v>1</v>
+      </c>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H414" t="n">
+        <v>3</v>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L414" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M414" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>(1188, 26)</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>(232, 26)</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>(186, 26)</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start']</t>
+        </is>
+      </c>
+      <c r="R414" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>454</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>3</v>
+      </c>
+      <c r="D415" t="b">
+        <v>0</v>
+      </c>
+      <c r="E415" t="b">
+        <v>1</v>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H415" t="n">
+        <v>3</v>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L415" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M415" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>(1305, 26)</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>(250, 26)</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>(200, 26)</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start']</t>
+        </is>
+      </c>
+      <c r="R415" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>455</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>3</v>
+      </c>
+      <c r="D416" t="b">
+        <v>0</v>
+      </c>
+      <c r="E416" t="b">
+        <v>1</v>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H416" t="n">
+        <v>3</v>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L416" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M416" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>(1200, 13)</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>(238, 13)</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>(190, 13)</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start']</t>
+        </is>
+      </c>
+      <c r="R416" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>456</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>3</v>
+      </c>
+      <c r="D417" t="b">
+        <v>0</v>
+      </c>
+      <c r="E417" t="b">
+        <v>1</v>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H417" t="n">
+        <v>3</v>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L417" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M417" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>(1374, 13)</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>(255, 13)</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>(204, 13)</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start']</t>
+        </is>
+      </c>
+      <c r="R417" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>457</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>3</v>
+      </c>
+      <c r="D418" t="b">
+        <v>0</v>
+      </c>
+      <c r="E418" t="b">
+        <v>1</v>
+      </c>
+      <c r="F418" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="n">
+        <v>5</v>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L418" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M418" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>(660, 32)</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>(122, 32)</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>(98, 32)</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R418" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>458</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>3</v>
+      </c>
+      <c r="D419" t="b">
+        <v>0</v>
+      </c>
+      <c r="E419" t="b">
+        <v>1</v>
+      </c>
+      <c r="F419" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="n">
+        <v>5</v>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L419" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M419" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>(2076, 32)</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>(403, 32)</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>(322, 32)</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R419" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>459</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>3</v>
+      </c>
+      <c r="D420" t="b">
+        <v>0</v>
+      </c>
+      <c r="E420" t="b">
+        <v>1</v>
+      </c>
+      <c r="F420" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G420" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H420" t="n">
+        <v>5</v>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L420" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M420" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>(1068, 24)</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>(201, 24)</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>(161, 24)</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_KGP', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R420" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>460</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>3</v>
+      </c>
+      <c r="D421" t="b">
+        <v>0</v>
+      </c>
+      <c r="E421" t="b">
+        <v>1</v>
+      </c>
+      <c r="F421" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G421" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H421" t="n">
+        <v>5</v>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L421" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M421" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>(2211, 24)</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>(441, 24)</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>(353, 24)</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_KGP', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R421" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>461</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>3</v>
+      </c>
+      <c r="D422" t="b">
+        <v>0</v>
+      </c>
+      <c r="E422" t="b">
+        <v>1</v>
+      </c>
+      <c r="F422" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G422" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H422" t="n">
+        <v>5</v>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L422" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M422" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>(1365, 16)</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>(256, 16)</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>(205, 16)</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R422" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>462</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>3</v>
+      </c>
+      <c r="D423" t="b">
+        <v>0</v>
+      </c>
+      <c r="E423" t="b">
+        <v>1</v>
+      </c>
+      <c r="F423" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G423" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H423" t="n">
+        <v>5</v>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L423" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M423" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>(2253, 16)</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>(442, 16)</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>(353, 16)</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R423" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>463</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>3</v>
+      </c>
+      <c r="D424" t="b">
+        <v>0</v>
+      </c>
+      <c r="E424" t="b">
+        <v>1</v>
+      </c>
+      <c r="F424" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G424" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H424" t="n">
+        <v>5</v>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L424" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M424" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>(1974, 8)</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>(408, 8)</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>(327, 8)</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_attacks', 'dif_mean_rat_player_start', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R424" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>464</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>3</v>
+      </c>
+      <c r="D425" t="b">
+        <v>0</v>
+      </c>
+      <c r="E425" t="b">
+        <v>1</v>
+      </c>
+      <c r="F425" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G425" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H425" t="n">
+        <v>5</v>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L425" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M425" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>(2433, 8)</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>(478, 8)</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>(382, 8)</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_attacks', 'dif_mean_rat_player_start', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R425" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>465</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>3</v>
+      </c>
+      <c r="D426" t="b">
+        <v>0</v>
+      </c>
+      <c r="E426" t="b">
+        <v>1</v>
+      </c>
+      <c r="F426" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="n">
+        <v>5</v>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L426" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M426" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>(636, 46)</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>(121, 46)</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>(97, 46)</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R426" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>466</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>3</v>
+      </c>
+      <c r="D427" t="b">
+        <v>0</v>
+      </c>
+      <c r="E427" t="b">
+        <v>1</v>
+      </c>
+      <c r="F427" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="n">
+        <v>5</v>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L427" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M427" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>(2148, 46)</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>(415, 46)</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>(332, 46)</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R427" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>467</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>3</v>
+      </c>
+      <c r="D428" t="b">
+        <v>0</v>
+      </c>
+      <c r="E428" t="b">
+        <v>1</v>
+      </c>
+      <c r="F428" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G428" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H428" t="n">
+        <v>5</v>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L428" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M428" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>(771, 34)</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>(146, 34)</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>(117, 34)</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R428" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>468</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>3</v>
+      </c>
+      <c r="D429" t="b">
+        <v>0</v>
+      </c>
+      <c r="E429" t="b">
+        <v>1</v>
+      </c>
+      <c r="F429" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G429" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H429" t="n">
+        <v>5</v>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L429" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M429" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>(2244, 34)</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>(441, 34)</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>(353, 34)</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R429" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>469</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>3</v>
+      </c>
+      <c r="D430" t="b">
+        <v>0</v>
+      </c>
+      <c r="E430" t="b">
+        <v>1</v>
+      </c>
+      <c r="F430" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G430" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H430" t="n">
+        <v>5</v>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L430" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M430" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>(1458, 23)</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>(279, 23)</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>(223, 23)</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R430" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>470</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>3</v>
+      </c>
+      <c r="D431" t="b">
+        <v>0</v>
+      </c>
+      <c r="E431" t="b">
+        <v>1</v>
+      </c>
+      <c r="F431" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G431" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H431" t="n">
+        <v>5</v>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L431" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M431" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>(2274, 23)</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>(442, 23)</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>(353, 23)</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R431" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>471</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>3</v>
+      </c>
+      <c r="D432" t="b">
+        <v>0</v>
+      </c>
+      <c r="E432" t="b">
+        <v>1</v>
+      </c>
+      <c r="F432" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G432" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H432" t="n">
+        <v>5</v>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L432" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M432" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>(2043, 12)</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>(406, 12)</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>(325, 12)</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_sub', 'dif_mean_pot_player_sub']</t>
+        </is>
+      </c>
+      <c r="R432" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>472</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>3</v>
+      </c>
+      <c r="D433" t="b">
+        <v>0</v>
+      </c>
+      <c r="E433" t="b">
+        <v>1</v>
+      </c>
+      <c r="F433" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G433" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H433" t="n">
+        <v>5</v>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L433" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M433" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>(2220, 12)</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>(442, 12)</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>(353, 12)</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_sub', 'dif_mean_pot_player_sub']</t>
+        </is>
+      </c>
+      <c r="R433" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>473</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>3</v>
+      </c>
+      <c r="D434" t="b">
+        <v>0</v>
+      </c>
+      <c r="E434" t="b">
+        <v>1</v>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="n">
+        <v>5</v>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L434" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M434" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>(627, 52)</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>(120, 52)</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>(96, 52)</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R434" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>474</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>3</v>
+      </c>
+      <c r="D435" t="b">
+        <v>0</v>
+      </c>
+      <c r="E435" t="b">
+        <v>1</v>
+      </c>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="n">
+        <v>5</v>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L435" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M435" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>(2055, 52)</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>(401, 52)</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>(321, 52)</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R435" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>475</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>3</v>
+      </c>
+      <c r="D436" t="b">
+        <v>0</v>
+      </c>
+      <c r="E436" t="b">
+        <v>1</v>
+      </c>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H436" t="n">
+        <v>5</v>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L436" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M436" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>(708, 39)</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>(135, 39)</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>(108, 39)</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R436" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>476</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>3</v>
+      </c>
+      <c r="D437" t="b">
+        <v>0</v>
+      </c>
+      <c r="E437" t="b">
+        <v>1</v>
+      </c>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H437" t="n">
+        <v>5</v>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L437" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M437" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>(2121, 39)</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>(424, 39)</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>(339, 39)</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R437" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>477</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>3</v>
+      </c>
+      <c r="D438" t="b">
+        <v>0</v>
+      </c>
+      <c r="E438" t="b">
+        <v>1</v>
+      </c>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H438" t="n">
+        <v>5</v>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L438" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M438" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>(1377, 26)</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>(258, 26)</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>(207, 26)</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R438" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>478</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>3</v>
+      </c>
+      <c r="D439" t="b">
+        <v>0</v>
+      </c>
+      <c r="E439" t="b">
+        <v>1</v>
+      </c>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H439" t="n">
+        <v>5</v>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L439" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M439" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>(2301, 26)</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>(442, 26)</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>(353, 26)</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R439" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>479</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>3</v>
+      </c>
+      <c r="D440" t="b">
+        <v>0</v>
+      </c>
+      <c r="E440" t="b">
+        <v>1</v>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H440" t="n">
+        <v>5</v>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L440" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M440" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>(1989, 13)</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>(403, 13)</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>(323, 13)</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R440" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>480</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>3</v>
+      </c>
+      <c r="D441" t="b">
+        <v>0</v>
+      </c>
+      <c r="E441" t="b">
+        <v>1</v>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H441" t="n">
+        <v>5</v>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L441" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M441" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>(2001, 13)</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>(405, 13)</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>(324, 13)</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R441" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>481</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>3</v>
+      </c>
+      <c r="D442" t="b">
+        <v>0</v>
+      </c>
+      <c r="E442" t="b">
+        <v>1</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="n">
+        <v>10</v>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L442" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M442" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>(1482, 25)</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>(298, 25)</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>(238, 25)</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R442" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>482</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>3</v>
+      </c>
+      <c r="D443" t="b">
+        <v>0</v>
+      </c>
+      <c r="E443" t="b">
+        <v>1</v>
+      </c>
+      <c r="F443" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="n">
+        <v>10</v>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L443" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M443" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>(4686, 25)</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>(899, 25)</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>(719, 25)</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R443" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>483</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>3</v>
+      </c>
+      <c r="D444" t="b">
+        <v>0</v>
+      </c>
+      <c r="E444" t="b">
+        <v>1</v>
+      </c>
+      <c r="F444" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G444" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H444" t="n">
+        <v>10</v>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L444" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M444" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>(2481, 19)</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>(478, 19)</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>(383, 19)</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_KGP', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R444" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>484</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>3</v>
+      </c>
+      <c r="D445" t="b">
+        <v>0</v>
+      </c>
+      <c r="E445" t="b">
+        <v>1</v>
+      </c>
+      <c r="F445" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G445" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H445" t="n">
+        <v>10</v>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L445" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M445" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>(4917, 19)</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>(934, 19)</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>(747, 19)</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_KGP', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R445" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>485</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>3</v>
+      </c>
+      <c r="D446" t="b">
+        <v>0</v>
+      </c>
+      <c r="E446" t="b">
+        <v>1</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G446" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H446" t="n">
+        <v>10</v>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L446" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M446" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>(2490, 13)</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>(489, 13)</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>(392, 13)</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_KGP', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R446" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>486</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>3</v>
+      </c>
+      <c r="D447" t="b">
+        <v>0</v>
+      </c>
+      <c r="E447" t="b">
+        <v>1</v>
+      </c>
+      <c r="F447" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G447" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H447" t="n">
+        <v>10</v>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L447" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M447" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>(4692, 13)</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>(921, 13)</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>(737, 13)</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_KGP', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R447" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>487</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>3</v>
+      </c>
+      <c r="D448" t="b">
+        <v>0</v>
+      </c>
+      <c r="E448" t="b">
+        <v>1</v>
+      </c>
+      <c r="F448" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G448" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H448" t="n">
+        <v>10</v>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L448" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M448" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>(4605, 7)</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>(879, 7)</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>(704, 7)</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_rat_player_start']</t>
+        </is>
+      </c>
+      <c r="R448" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>488</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>3</v>
+      </c>
+      <c r="D449" t="b">
+        <v>0</v>
+      </c>
+      <c r="E449" t="b">
+        <v>1</v>
+      </c>
+      <c r="F449" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G449" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H449" t="n">
+        <v>10</v>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L449" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M449" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>(5217, 7)</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>(995, 7)</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>(796, 7)</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_rat_player_start']</t>
+        </is>
+      </c>
+      <c r="R449" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>489</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>3</v>
+      </c>
+      <c r="D450" t="b">
+        <v>0</v>
+      </c>
+      <c r="E450" t="b">
+        <v>1</v>
+      </c>
+      <c r="F450" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="n">
+        <v>10</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L450" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M450" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>(1338, 41)</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>(269, 41)</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>(215, 41)</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R450" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>490</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>3</v>
+      </c>
+      <c r="D451" t="b">
+        <v>0</v>
+      </c>
+      <c r="E451" t="b">
+        <v>1</v>
+      </c>
+      <c r="F451" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="n">
+        <v>10</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L451" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M451" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>(4395, 41)</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>(844, 41)</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>(675, 41)</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R451" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>491</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>3</v>
+      </c>
+      <c r="D452" t="b">
+        <v>0</v>
+      </c>
+      <c r="E452" t="b">
+        <v>1</v>
+      </c>
+      <c r="F452" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G452" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H452" t="n">
+        <v>10</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L452" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M452" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>(2694, 31)</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>(530, 31)</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>(424, 31)</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>['referee', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R452" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>492</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>3</v>
+      </c>
+      <c r="D453" t="b">
+        <v>0</v>
+      </c>
+      <c r="E453" t="b">
+        <v>1</v>
+      </c>
+      <c r="F453" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G453" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H453" t="n">
+        <v>10</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L453" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M453" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>(4497, 31)</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>(856, 31)</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>(685, 31)</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>['referee', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R453" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>493</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>3</v>
+      </c>
+      <c r="D454" t="b">
+        <v>0</v>
+      </c>
+      <c r="E454" t="b">
+        <v>1</v>
+      </c>
+      <c r="F454" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G454" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H454" t="n">
+        <v>10</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L454" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M454" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>(3036, 21)</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>(596, 21)</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>(477, 21)</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R454" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>494</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>3</v>
+      </c>
+      <c r="D455" t="b">
+        <v>0</v>
+      </c>
+      <c r="E455" t="b">
+        <v>1</v>
+      </c>
+      <c r="F455" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G455" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H455" t="n">
+        <v>10</v>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L455" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M455" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>(4917, 21)</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>(940, 21)</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>(752, 21)</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R455" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>495</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>3</v>
+      </c>
+      <c r="D456" t="b">
+        <v>0</v>
+      </c>
+      <c r="E456" t="b">
+        <v>1</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G456" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H456" t="n">
+        <v>10</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L456" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M456" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>(4368, 11)</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>(856, 11)</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>(685, 11)</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R456" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>496</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>3</v>
+      </c>
+      <c r="D457" t="b">
+        <v>0</v>
+      </c>
+      <c r="E457" t="b">
+        <v>1</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G457" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H457" t="n">
+        <v>10</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L457" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M457" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>(4998, 11)</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>(940, 11)</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>(752, 11)</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R457" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>497</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>3</v>
+      </c>
+      <c r="D458" t="b">
+        <v>0</v>
+      </c>
+      <c r="E458" t="b">
+        <v>1</v>
+      </c>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="n">
+        <v>10</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L458" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M458" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>(762, 47)</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>(164, 47)</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>(132, 47)</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R458" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>498</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>3</v>
+      </c>
+      <c r="D459" t="b">
+        <v>0</v>
+      </c>
+      <c r="E459" t="b">
+        <v>1</v>
+      </c>
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="n">
+        <v>10</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L459" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M459" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>(4404, 47)</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>(659, 47)</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>(652, 47)</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R459" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>499</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>3</v>
+      </c>
+      <c r="D460" t="b">
+        <v>0</v>
+      </c>
+      <c r="E460" t="b">
+        <v>1</v>
+      </c>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H460" t="n">
+        <v>10</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L460" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M460" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>(1398, 35)</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>(292, 35)</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>(234, 35)</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>['referee', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R460" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>500</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>3</v>
+      </c>
+      <c r="D461" t="b">
+        <v>0</v>
+      </c>
+      <c r="E461" t="b">
+        <v>1</v>
+      </c>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H461" t="n">
+        <v>10</v>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L461" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M461" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>(4386, 35)</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>(827, 35)</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>(662, 35)</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>['referee', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R461" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>501</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>3</v>
+      </c>
+      <c r="D462" t="b">
+        <v>0</v>
+      </c>
+      <c r="E462" t="b">
+        <v>1</v>
+      </c>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H462" t="n">
+        <v>10</v>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L462" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M462" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>(1938, 24)</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>(389, 24)</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>(311, 24)</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R462" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>502</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>3</v>
+      </c>
+      <c r="D463" t="b">
+        <v>0</v>
+      </c>
+      <c r="E463" t="b">
+        <v>1</v>
+      </c>
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H463" t="n">
+        <v>10</v>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L463" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M463" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>(4758, 24)</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>(909, 24)</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>(727, 24)</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R463" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>503</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>3</v>
+      </c>
+      <c r="D464" t="b">
+        <v>0</v>
+      </c>
+      <c r="E464" t="b">
+        <v>1</v>
+      </c>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H464" t="n">
+        <v>10</v>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L464" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M464" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>(4284, 12)</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>(836, 12)</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>(669, 12)</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_rat_player_start', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start']</t>
+        </is>
+      </c>
+      <c r="R464" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>504</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>3</v>
+      </c>
+      <c r="D465" t="b">
+        <v>0</v>
+      </c>
+      <c r="E465" t="b">
+        <v>1</v>
+      </c>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H465" t="n">
+        <v>10</v>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L465" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M465" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>(4749, 12)</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>(909, 12)</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>(727, 12)</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_rat_player_start', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start']</t>
+        </is>
+      </c>
+      <c r="R465" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>506</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>3</v>
+      </c>
+      <c r="D466" t="b">
+        <v>0</v>
+      </c>
+      <c r="E466" t="b">
+        <v>0</v>
+      </c>
+      <c r="F466" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="n">
+        <v>3</v>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L466" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M466" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>(1236, 54)</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>(234, 54)</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>(187, 54)</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R466" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>507</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>3</v>
+      </c>
+      <c r="D467" t="b">
+        <v>0</v>
+      </c>
+      <c r="E467" t="b">
+        <v>0</v>
+      </c>
+      <c r="F467" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G467" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H467" t="n">
+        <v>3</v>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L467" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M467" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>(819, 40)</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>(150, 40)</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>(120, 40)</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R467" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>508</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>3</v>
+      </c>
+      <c r="D468" t="b">
+        <v>0</v>
+      </c>
+      <c r="E468" t="b">
+        <v>0</v>
+      </c>
+      <c r="F468" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G468" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H468" t="n">
+        <v>3</v>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L468" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M468" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>(1284, 40)</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>(244, 40)</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>(195, 40)</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R468" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>509</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>3</v>
+      </c>
+      <c r="D469" t="b">
+        <v>0</v>
+      </c>
+      <c r="E469" t="b">
+        <v>0</v>
+      </c>
+      <c r="F469" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G469" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H469" t="n">
+        <v>3</v>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L469" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M469" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>(900, 27)</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>(165, 27)</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>(132, 27)</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R469" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>510</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>3</v>
+      </c>
+      <c r="D470" t="b">
+        <v>0</v>
+      </c>
+      <c r="E470" t="b">
+        <v>0</v>
+      </c>
+      <c r="F470" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G470" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H470" t="n">
+        <v>3</v>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L470" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M470" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>(1236, 27)</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>(244, 27)</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>(195, 27)</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R470" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>511</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>3</v>
+      </c>
+      <c r="D471" t="b">
+        <v>0</v>
+      </c>
+      <c r="E471" t="b">
+        <v>0</v>
+      </c>
+      <c r="F471" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G471" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H471" t="n">
+        <v>3</v>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L471" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M471" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>(966, 14)</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>(181, 14)</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>(145, 14)</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start']</t>
+        </is>
+      </c>
+      <c r="R471" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>512</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>3</v>
+      </c>
+      <c r="D472" t="b">
+        <v>0</v>
+      </c>
+      <c r="E472" t="b">
+        <v>0</v>
+      </c>
+      <c r="F472" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G472" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H472" t="n">
+        <v>3</v>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L472" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M472" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>(1500, 14)</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>(282, 14)</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>(226, 14)</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start']</t>
+        </is>
+      </c>
+      <c r="R472" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>514</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>3</v>
+      </c>
+      <c r="D473" t="b">
+        <v>0</v>
+      </c>
+      <c r="E473" t="b">
+        <v>0</v>
+      </c>
+      <c r="F473" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="n">
+        <v>3</v>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L473" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M473" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>(1314, 80)</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>(244, 80)</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>(195, 80)</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R473" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>516</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>3</v>
+      </c>
+      <c r="D474" t="b">
+        <v>0</v>
+      </c>
+      <c r="E474" t="b">
+        <v>0</v>
+      </c>
+      <c r="F474" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G474" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H474" t="n">
+        <v>3</v>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L474" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M474" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>(1275, 60)</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>(244, 60)</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>(195, 60)</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R474" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>517</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>3</v>
+      </c>
+      <c r="D475" t="b">
+        <v>0</v>
+      </c>
+      <c r="E475" t="b">
+        <v>0</v>
+      </c>
+      <c r="F475" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G475" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H475" t="n">
+        <v>3</v>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L475" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M475" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>(894, 40)</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>(163, 40)</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>(130, 40)</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R475" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>518</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>3</v>
+      </c>
+      <c r="D476" t="b">
+        <v>0</v>
+      </c>
+      <c r="E476" t="b">
+        <v>0</v>
+      </c>
+      <c r="F476" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G476" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H476" t="n">
+        <v>3</v>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L476" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M476" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>(1299, 40)</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>(244, 40)</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>(195, 40)</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R476" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>519</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>3</v>
+      </c>
+      <c r="D477" t="b">
+        <v>0</v>
+      </c>
+      <c r="E477" t="b">
+        <v>0</v>
+      </c>
+      <c r="F477" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G477" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H477" t="n">
+        <v>3</v>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L477" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M477" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>(1005, 20)</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>(185, 20)</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>(148, 20)</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R477" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>520</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>3</v>
+      </c>
+      <c r="D478" t="b">
+        <v>0</v>
+      </c>
+      <c r="E478" t="b">
+        <v>0</v>
+      </c>
+      <c r="F478" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G478" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H478" t="n">
+        <v>3</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L478" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M478" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>(1281, 20)</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>(250, 20)</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>(200, 20)</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R478" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>522</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>3</v>
+      </c>
+      <c r="D479" t="b">
+        <v>0</v>
+      </c>
+      <c r="E479" t="b">
+        <v>0</v>
+      </c>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="n">
+        <v>3</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L479" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M479" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>(1272, 89)</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>(244, 89)</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>(195, 89)</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R479" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>524</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>3</v>
+      </c>
+      <c r="D480" t="b">
+        <v>0</v>
+      </c>
+      <c r="E480" t="b">
+        <v>0</v>
+      </c>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H480" t="n">
+        <v>3</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L480" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M480" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>(1296, 67)</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>(244, 67)</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>(195, 67)</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R480" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>525</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>3</v>
+      </c>
+      <c r="D481" t="b">
+        <v>0</v>
+      </c>
+      <c r="E481" t="b">
+        <v>0</v>
+      </c>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H481" t="n">
+        <v>3</v>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L481" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M481" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>(855, 45)</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>(160, 45)</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>(128, 45)</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R481" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>526</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>3</v>
+      </c>
+      <c r="D482" t="b">
+        <v>0</v>
+      </c>
+      <c r="E482" t="b">
+        <v>0</v>
+      </c>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H482" t="n">
+        <v>3</v>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L482" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M482" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>(1281, 45)</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>(244, 45)</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>(195, 45)</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R482" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>527</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>3</v>
+      </c>
+      <c r="D483" t="b">
+        <v>0</v>
+      </c>
+      <c r="E483" t="b">
+        <v>0</v>
+      </c>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H483" t="n">
+        <v>3</v>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L483" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M483" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>(1194, 23)</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>(232, 23)</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>(186, 23)</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start']</t>
+        </is>
+      </c>
+      <c r="R483" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>528</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>3</v>
+      </c>
+      <c r="D484" t="b">
+        <v>0</v>
+      </c>
+      <c r="E484" t="b">
+        <v>0</v>
+      </c>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H484" t="n">
+        <v>3</v>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L484" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M484" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>(1305, 23)</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>(250, 23)</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>(200, 23)</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start']</t>
+        </is>
+      </c>
+      <c r="R484" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>529</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>3</v>
+      </c>
+      <c r="D485" t="b">
+        <v>0</v>
+      </c>
+      <c r="E485" t="b">
+        <v>0</v>
+      </c>
+      <c r="F485" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="n">
+        <v>5</v>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L485" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M485" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>(768, 55)</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>(142, 55)</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>(114, 55)</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R485" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>530</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>3</v>
+      </c>
+      <c r="D486" t="b">
+        <v>0</v>
+      </c>
+      <c r="E486" t="b">
+        <v>0</v>
+      </c>
+      <c r="F486" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G486" t="inlineStr"/>
+      <c r="H486" t="n">
+        <v>5</v>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L486" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M486" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>(2103, 55)</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>(415, 55)</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>(332, 55)</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R486" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>531</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>3</v>
+      </c>
+      <c r="D487" t="b">
+        <v>0</v>
+      </c>
+      <c r="E487" t="b">
+        <v>0</v>
+      </c>
+      <c r="F487" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G487" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H487" t="n">
+        <v>5</v>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L487" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M487" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>(765, 41)</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>(142, 41)</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>(114, 41)</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R487" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>532</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>3</v>
+      </c>
+      <c r="D488" t="b">
+        <v>0</v>
+      </c>
+      <c r="E488" t="b">
+        <v>0</v>
+      </c>
+      <c r="F488" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G488" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H488" t="n">
+        <v>5</v>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L488" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M488" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>(2157, 41)</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>(424, 41)</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>(339, 41)</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R488" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>533</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>3</v>
+      </c>
+      <c r="D489" t="b">
+        <v>0</v>
+      </c>
+      <c r="E489" t="b">
+        <v>0</v>
+      </c>
+      <c r="F489" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G489" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H489" t="n">
+        <v>5</v>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L489" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M489" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>(738, 28)</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>(142, 28)</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>(114, 28)</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R489" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>534</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>3</v>
+      </c>
+      <c r="D490" t="b">
+        <v>0</v>
+      </c>
+      <c r="E490" t="b">
+        <v>0</v>
+      </c>
+      <c r="F490" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G490" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H490" t="n">
+        <v>5</v>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L490" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M490" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>(2169, 28)</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>(424, 28)</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>(339, 28)</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R490" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>535</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>3</v>
+      </c>
+      <c r="D491" t="b">
+        <v>0</v>
+      </c>
+      <c r="E491" t="b">
+        <v>0</v>
+      </c>
+      <c r="F491" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G491" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H491" t="n">
+        <v>5</v>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L491" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M491" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>(1308, 14)</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>(259, 14)</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>(207, 14)</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R491" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>536</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>3</v>
+      </c>
+      <c r="D492" t="b">
+        <v>0</v>
+      </c>
+      <c r="E492" t="b">
+        <v>0</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G492" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H492" t="n">
+        <v>5</v>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L492" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M492" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>(2439, 14)</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>(478, 14)</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>(382, 14)</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rep_player_sub']</t>
+        </is>
+      </c>
+      <c r="R492" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>538</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>3</v>
+      </c>
+      <c r="D493" t="b">
+        <v>0</v>
+      </c>
+      <c r="E493" t="b">
+        <v>0</v>
+      </c>
+      <c r="F493" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G493" t="inlineStr"/>
+      <c r="H493" t="n">
+        <v>5</v>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L493" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M493" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>(2118, 81)</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>(413, 81)</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>(331, 81)</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R493" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>539</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>3</v>
+      </c>
+      <c r="D494" t="b">
+        <v>0</v>
+      </c>
+      <c r="E494" t="b">
+        <v>0</v>
+      </c>
+      <c r="F494" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G494" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H494" t="n">
+        <v>5</v>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L494" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M494" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>(699, 61)</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>(128, 61)</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>(102, 61)</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R494" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>540</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>3</v>
+      </c>
+      <c r="D495" t="b">
+        <v>0</v>
+      </c>
+      <c r="E495" t="b">
+        <v>0</v>
+      </c>
+      <c r="F495" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G495" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H495" t="n">
+        <v>5</v>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L495" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M495" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>(2142, 61)</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>(415, 61)</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>(332, 61)</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R495" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>541</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>3</v>
+      </c>
+      <c r="D496" t="b">
+        <v>0</v>
+      </c>
+      <c r="E496" t="b">
+        <v>0</v>
+      </c>
+      <c r="F496" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G496" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H496" t="n">
+        <v>5</v>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L496" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M496" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>(1329, 41)</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>(244, 41)</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>(195, 41)</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R496" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>542</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>3</v>
+      </c>
+      <c r="D497" t="b">
+        <v>0</v>
+      </c>
+      <c r="E497" t="b">
+        <v>0</v>
+      </c>
+      <c r="F497" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G497" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H497" t="n">
+        <v>5</v>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L497" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M497" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>(2418, 41)</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>(477, 41)</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>(382, 41)</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R497" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>543</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>3</v>
+      </c>
+      <c r="D498" t="b">
+        <v>0</v>
+      </c>
+      <c r="E498" t="b">
+        <v>0</v>
+      </c>
+      <c r="F498" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G498" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H498" t="n">
+        <v>5</v>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L498" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M498" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>(2055, 21)</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>(406, 21)</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>(325, 21)</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R498" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>544</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>3</v>
+      </c>
+      <c r="D499" t="b">
+        <v>0</v>
+      </c>
+      <c r="E499" t="b">
+        <v>0</v>
+      </c>
+      <c r="F499" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G499" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H499" t="n">
+        <v>5</v>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L499" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M499" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>(2220, 21)</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>(442, 21)</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>(353, 21)</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R499" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>546</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>3</v>
+      </c>
+      <c r="D500" t="b">
+        <v>0</v>
+      </c>
+      <c r="E500" t="b">
+        <v>0</v>
+      </c>
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="inlineStr"/>
+      <c r="H500" t="n">
+        <v>5</v>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L500" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M500" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>(2040, 89)</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>(401, 89)</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>(321, 89)</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R500" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>548</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>3</v>
+      </c>
+      <c r="D501" t="b">
+        <v>0</v>
+      </c>
+      <c r="E501" t="b">
+        <v>0</v>
+      </c>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H501" t="n">
+        <v>5</v>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L501" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M501" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>(2157, 67)</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>(422, 67)</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>(337, 67)</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R501" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>549</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>3</v>
+      </c>
+      <c r="D502" t="b">
+        <v>0</v>
+      </c>
+      <c r="E502" t="b">
+        <v>0</v>
+      </c>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H502" t="n">
+        <v>5</v>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L502" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M502" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>(702, 45)</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>(129, 45)</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>(104, 45)</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R502" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>550</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>3</v>
+      </c>
+      <c r="D503" t="b">
+        <v>0</v>
+      </c>
+      <c r="E503" t="b">
+        <v>0</v>
+      </c>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H503" t="n">
+        <v>5</v>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L503" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M503" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>(2175, 45)</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>(424, 45)</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>(339, 45)</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R503" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>551</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>3</v>
+      </c>
+      <c r="D504" t="b">
+        <v>0</v>
+      </c>
+      <c r="E504" t="b">
+        <v>0</v>
+      </c>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H504" t="n">
+        <v>5</v>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L504" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M504" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>(1947, 23)</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>(403, 23)</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>(323, 23)</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R504" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>552</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>3</v>
+      </c>
+      <c r="D505" t="b">
+        <v>0</v>
+      </c>
+      <c r="E505" t="b">
+        <v>0</v>
+      </c>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H505" t="n">
+        <v>5</v>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L505" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M505" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>(2253, 23)</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>(442, 23)</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>(353, 23)</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>['dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R505" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>553</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>3</v>
+      </c>
+      <c r="D506" t="b">
+        <v>0</v>
+      </c>
+      <c r="E506" t="b">
+        <v>0</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G506" t="inlineStr"/>
+      <c r="H506" t="n">
+        <v>10</v>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L506" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M506" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>(1524, 48)</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>(298, 48)</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>(238, 48)</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R506" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>554</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>3</v>
+      </c>
+      <c r="D507" t="b">
+        <v>0</v>
+      </c>
+      <c r="E507" t="b">
+        <v>0</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G507" t="inlineStr"/>
+      <c r="H507" t="n">
+        <v>10</v>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L507" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M507" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>(4467, 48)</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>(851, 48)</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>(681, 48)</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_hei_player_start']</t>
+        </is>
+      </c>
+      <c r="R507" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>555</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>3</v>
+      </c>
+      <c r="D508" t="b">
+        <v>0</v>
+      </c>
+      <c r="E508" t="b">
+        <v>0</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G508" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H508" t="n">
+        <v>10</v>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L508" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M508" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>(1530, 36)</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>(298, 36)</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>(238, 36)</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R508" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>556</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>3</v>
+      </c>
+      <c r="D509" t="b">
+        <v>0</v>
+      </c>
+      <c r="E509" t="b">
+        <v>0</v>
+      </c>
+      <c r="F509" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G509" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H509" t="n">
+        <v>10</v>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L509" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M509" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>(4515, 36)</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>(865, 36)</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>(692, 36)</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R509" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>557</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>3</v>
+      </c>
+      <c r="D510" t="b">
+        <v>0</v>
+      </c>
+      <c r="E510" t="b">
+        <v>0</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G510" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H510" t="n">
+        <v>10</v>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L510" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M510" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>(2874, 24)</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>(575, 24)</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>(460, 24)</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R510" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>558</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>3</v>
+      </c>
+      <c r="D511" t="b">
+        <v>0</v>
+      </c>
+      <c r="E511" t="b">
+        <v>0</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G511" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H511" t="n">
+        <v>10</v>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L511" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M511" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>(4920, 24)</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>(956, 24)</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>(765, 24)</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub']</t>
+        </is>
+      </c>
+      <c r="R511" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>559</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>3</v>
+      </c>
+      <c r="D512" t="b">
+        <v>0</v>
+      </c>
+      <c r="E512" t="b">
+        <v>0</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G512" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H512" t="n">
+        <v>10</v>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L512" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M512" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>(2958, 12)</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>(575, 12)</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>(460, 12)</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_rat_player_start']</t>
+        </is>
+      </c>
+      <c r="R512" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>560</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>3</v>
+      </c>
+      <c r="D513" t="b">
+        <v>0</v>
+      </c>
+      <c r="E513" t="b">
+        <v>0</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G513" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H513" t="n">
+        <v>10</v>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L513" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M513" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>(5019, 12)</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>(956, 12)</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>(765, 12)</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_rat_player_start']</t>
+        </is>
+      </c>
+      <c r="R513" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>561</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>3</v>
+      </c>
+      <c r="D514" t="b">
+        <v>0</v>
+      </c>
+      <c r="E514" t="b">
+        <v>0</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G514" t="inlineStr"/>
+      <c r="H514" t="n">
+        <v>10</v>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L514" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M514" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>(1341, 69)</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>(269, 69)</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>(215, 69)</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R514" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>562</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>3</v>
+      </c>
+      <c r="D515" t="b">
+        <v>0</v>
+      </c>
+      <c r="E515" t="b">
+        <v>0</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G515" t="inlineStr"/>
+      <c r="H515" t="n">
+        <v>10</v>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L515" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M515" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>(4215, 69)</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>(808, 69)</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>(646, 69)</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R515" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>563</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>3</v>
+      </c>
+      <c r="D516" t="b">
+        <v>0</v>
+      </c>
+      <c r="E516" t="b">
+        <v>0</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G516" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H516" t="n">
+        <v>10</v>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L516" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M516" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>(2220, 52)</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>(438, 52)</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>(350, 52)</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R516" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>564</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>3</v>
+      </c>
+      <c r="D517" t="b">
+        <v>0</v>
+      </c>
+      <c r="E517" t="b">
+        <v>0</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G517" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H517" t="n">
+        <v>10</v>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L517" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M517" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>(4614, 52)</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>(891, 52)</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>(713, 52)</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R517" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>565</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>3</v>
+      </c>
+      <c r="D518" t="b">
+        <v>0</v>
+      </c>
+      <c r="E518" t="b">
+        <v>0</v>
+      </c>
+      <c r="F518" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G518" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H518" t="n">
+        <v>10</v>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L518" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M518" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>(2697, 35)</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>(530, 35)</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>(424, 35)</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R518" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>566</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>3</v>
+      </c>
+      <c r="D519" t="b">
+        <v>0</v>
+      </c>
+      <c r="E519" t="b">
+        <v>0</v>
+      </c>
+      <c r="F519" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G519" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H519" t="n">
+        <v>10</v>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L519" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M519" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>(4743, 35)</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>(910, 35)</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>(728, 35)</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R519" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>567</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>3</v>
+      </c>
+      <c r="D520" t="b">
+        <v>0</v>
+      </c>
+      <c r="E520" t="b">
+        <v>0</v>
+      </c>
+      <c r="F520" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G520" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H520" t="n">
+        <v>10</v>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L520" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M520" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>(3006, 18)</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>(596, 18)</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>(477, 18)</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R520" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>568</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>3</v>
+      </c>
+      <c r="D521" t="b">
+        <v>0</v>
+      </c>
+      <c r="E521" t="b">
+        <v>0</v>
+      </c>
+      <c r="F521" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G521" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H521" t="n">
+        <v>10</v>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L521" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M521" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>(4917, 18)</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>(940, 18)</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>(752, 18)</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R521" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>570</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>3</v>
+      </c>
+      <c r="D522" t="b">
+        <v>0</v>
+      </c>
+      <c r="E522" t="b">
+        <v>0</v>
+      </c>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr"/>
+      <c r="H522" t="n">
+        <v>10</v>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L522" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M522" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>(4200, 78)</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>(688, 78)</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>(623, 78)</t>
+        </is>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_age_player_start', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_hei_player_start', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R522" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>571</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>3</v>
+      </c>
+      <c r="D523" t="b">
+        <v>0</v>
+      </c>
+      <c r="E523" t="b">
+        <v>0</v>
+      </c>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H523" t="n">
+        <v>10</v>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L523" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M523" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>(720, 58)</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>(164, 58)</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>(132, 58)</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R523" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>572</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>3</v>
+      </c>
+      <c r="D524" t="b">
+        <v>0</v>
+      </c>
+      <c r="E524" t="b">
+        <v>0</v>
+      </c>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H524" t="n">
+        <v>10</v>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L524" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M524" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>(4650, 58)</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>(627, 58)</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>(684, 58)</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R524" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>573</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>3</v>
+      </c>
+      <c r="D525" t="b">
+        <v>0</v>
+      </c>
+      <c r="E525" t="b">
+        <v>0</v>
+      </c>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H525" t="n">
+        <v>10</v>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L525" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M525" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>(1392, 39)</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>(292, 39)</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>(234, 39)</t>
+        </is>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R525" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>574</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>3</v>
+      </c>
+      <c r="D526" t="b">
+        <v>0</v>
+      </c>
+      <c r="E526" t="b">
+        <v>0</v>
+      </c>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H526" t="n">
+        <v>10</v>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L526" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M526" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>(4719, 39)</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>(910, 39)</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>(728, 39)</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_age_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R526" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>575</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>3</v>
+      </c>
+      <c r="D527" t="b">
+        <v>0</v>
+      </c>
+      <c r="E527" t="b">
+        <v>0</v>
+      </c>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H527" t="n">
+        <v>10</v>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L527" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M527" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>(2976, 20)</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>(601, 20)</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>(481, 20)</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R527" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>576</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>3</v>
+      </c>
+      <c r="D528" t="b">
+        <v>0</v>
+      </c>
+      <c r="E528" t="b">
+        <v>0</v>
+      </c>
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H528" t="n">
+        <v>10</v>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>[771, 772, 773, 774]</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L528" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M528" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>(4713, 20)</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>(885, 20)</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>(708, 20)</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_rat_player_start', 'dif_mean_rat_player_sub', 'dif_mean_value_player_start', 'dif_mean_value_player_sub', 'dif_mean_wage_player_start', 'dif_mean_rep_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_pot_player_start', 'dif_mean_rep_player_start']</t>
+        </is>
+      </c>
+      <c r="R528" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
